--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,196 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E8" s="3">
         <v>7000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,8 +858,8 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
@@ -867,59 +870,62 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>-100</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
       <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -953,58 +959,61 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-200</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
@@ -1039,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>700</v>
       </c>
       <c r="I12" s="3">
         <v>700</v>
       </c>
       <c r="J12" s="3">
+        <v>700</v>
+      </c>
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1500</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1257,8 +1276,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1266,21 +1285,21 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1296,8 +1315,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1329,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1397,14 +1419,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7800</v>
       </c>
-      <c r="G17" s="3">
-        <v>10700</v>
-      </c>
       <c r="H17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I17" s="3">
         <v>6100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-2200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>5400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1657,52 +1690,52 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>3200</v>
-      </c>
       <c r="H20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-300</v>
       </c>
       <c r="J20" s="3">
         <v>-300</v>
       </c>
       <c r="K20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-300</v>
       </c>
       <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-200</v>
+      <c r="P20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3">
         <v>-200</v>
       </c>
       <c r="S20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
@@ -1710,8 +1743,8 @@
       <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>100</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1722,8 +1755,8 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
@@ -1731,74 +1764,77 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,20 +1844,23 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1906,99 +1945,105 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2078,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-26100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2689,52 +2758,52 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H32" s="3">
+        <v>200</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>300</v>
       </c>
       <c r="J32" s="3">
         <v>300</v>
       </c>
       <c r="K32" s="3">
+        <v>300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>300</v>
       </c>
       <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>200</v>
+      <c r="P32" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3">
         <v>200</v>
       </c>
       <c r="S32" s="3">
+        <v>200</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
@@ -2742,8 +2811,8 @@
       <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>-100</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2754,8 +2823,8 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
@@ -2763,97 +2832,103 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-26100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-26100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,83 +3264,84 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E41" s="3">
         <v>22100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,62 +3440,65 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>800</v>
       </c>
       <c r="J43" s="3">
         <v>800</v>
       </c>
       <c r="K43" s="3">
+        <v>800</v>
+      </c>
+      <c r="L43" s="3">
         <v>5500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
-      </c>
-      <c r="M43" s="3">
-        <v>300</v>
       </c>
       <c r="N43" s="3">
         <v>300</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3419,8 +3511,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3437,25 +3529,28 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
-      </c>
-      <c r="H44" s="3">
-        <v>500</v>
       </c>
       <c r="I44" s="3">
         <v>500</v>
@@ -3464,22 +3559,22 @@
         <v>500</v>
       </c>
       <c r="K44" s="3">
+        <v>500</v>
+      </c>
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1200</v>
-      </c>
-      <c r="P44" s="3">
-        <v>1700</v>
       </c>
       <c r="Q44" s="3">
         <v>1700</v>
@@ -3488,11 +3583,11 @@
         <v>1700</v>
       </c>
       <c r="S44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T44" s="3">
         <v>400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,8 +3600,8 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -3523,83 +3618,86 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>800</v>
       </c>
       <c r="Q45" s="3">
         <v>800</v>
       </c>
       <c r="R45" s="3">
+        <v>800</v>
+      </c>
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
-      </c>
-      <c r="X45" s="3">
-        <v>200</v>
       </c>
       <c r="Y45" s="3">
         <v>200</v>
       </c>
       <c r="Z45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,83 +3707,86 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E46" s="3">
         <v>27200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>27500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,8 +3796,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3781,28 +3885,31 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>200</v>
       </c>
       <c r="F48" s="3">
         <v>200</v>
       </c>
       <c r="G48" s="3">
+        <v>200</v>
+      </c>
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -3811,7 +3918,7 @@
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
@@ -3820,22 +3927,22 @@
         <v>300</v>
       </c>
       <c r="O48" s="3">
+        <v>300</v>
+      </c>
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1400</v>
       </c>
       <c r="U48" s="3">
         <v>1400</v>
@@ -3844,19 +3951,19 @@
         <v>1400</v>
       </c>
       <c r="W48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X48" s="3">
         <v>800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>200</v>
       </c>
       <c r="Z48" s="3">
         <v>200</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>200</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -3867,37 +3974,40 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E49" s="3">
         <v>4200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>500</v>
       </c>
       <c r="M49" s="3">
         <v>500</v>
@@ -3906,13 +4016,13 @@
         <v>500</v>
       </c>
       <c r="O49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>600</v>
       </c>
       <c r="Q49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R49" s="3">
         <v>700</v>
@@ -3920,8 +4030,8 @@
       <c r="S49" s="3">
         <v>700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>700</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3935,8 +4045,8 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4167,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -4179,7 +4298,7 @@
         <v>100</v>
       </c>
       <c r="T52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -4188,20 +4307,20 @@
         <v>0</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,83 +4419,86 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E54" s="3">
         <v>31500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>28300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,83 +4576,84 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4533,55 +4663,58 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1500</v>
+        <v>5400</v>
       </c>
       <c r="E58" s="3">
         <v>1500</v>
       </c>
       <c r="F58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>700</v>
       </c>
       <c r="N58" s="3">
         <v>700</v>
       </c>
       <c r="O58" s="3">
+        <v>700</v>
+      </c>
+      <c r="P58" s="3">
         <v>300</v>
-      </c>
-      <c r="P58" s="3">
-        <v>200</v>
       </c>
       <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>200</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -4598,8 +4731,8 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4619,83 +4752,86 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1400</v>
       </c>
       <c r="K59" s="3">
         <v>1400</v>
       </c>
       <c r="L59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>600</v>
       </c>
       <c r="U59" s="3">
         <v>600</v>
       </c>
       <c r="V59" s="3">
+        <v>600</v>
+      </c>
+      <c r="W59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,83 +4841,86 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E60" s="3">
         <v>10400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,62 +4930,65 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>4200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6400</v>
-      </c>
-      <c r="O61" s="3">
-        <v>6800</v>
       </c>
       <c r="P61" s="3">
         <v>6800</v>
       </c>
       <c r="Q61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="R61" s="3">
         <v>4800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4877,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4886,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -4895,7 +5040,7 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -4910,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -4919,19 +5064,19 @@
         <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
@@ -4940,20 +5085,20 @@
         <v>100</v>
       </c>
       <c r="W62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>600</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,28 +5375,31 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E66" s="3">
         <v>14600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>9800</v>
       </c>
       <c r="J66" s="3">
         <v>9800</v>
@@ -5251,53 +5408,53 @@
         <v>9800</v>
       </c>
       <c r="L66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="M66" s="3">
         <v>10900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5577,17 +5744,17 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>21200</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>20400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>19700</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,83 +5853,86 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-104100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-101800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-101200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-105800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-103100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-104000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-101000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-99400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-94100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-95200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-89100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-87000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-92200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-78000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-73200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-64200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-61500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-56500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-53300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-45900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-19800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,83 +6209,86 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E76" s="3">
         <v>16900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>10600</v>
       </c>
       <c r="S76" s="3">
         <v>10600</v>
       </c>
       <c r="T76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="U76" s="3">
         <v>12300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-26100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,13 +6605,14 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -6423,19 +6621,19 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -6444,7 +6642,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -6459,7 +6657,7 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -6471,7 +6669,7 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -6491,11 +6689,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,13 +7261,14 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7060,28 +7280,28 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7099,22 +7319,22 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
@@ -7123,13 +7343,16 @@
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,13 +7526,16 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7318,26 +7547,26 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-3300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>700</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -7351,28 +7580,28 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-100</v>
       </c>
       <c r="X94" s="3">
         <v>-100</v>
       </c>
       <c r="Y94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
@@ -7381,13 +7610,16 @@
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,74 +8004,77 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>22000</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -7837,19 +8082,22 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>18000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>18000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7934,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="R102" s="3">
-        <v>300</v>
       </c>
       <c r="S102" s="3">
         <v>300</v>
       </c>
       <c r="T102" s="3">
+        <v>300</v>
+      </c>
+      <c r="U102" s="3">
         <v>-3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20100</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-2300</v>
       </c>
       <c r="Y102" s="3">
         <v>-2300</v>
       </c>
       <c r="Z102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16600</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,202 +656,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>500</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,8 +865,8 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
@@ -873,62 +877,65 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-100</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
       <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,61 +969,64 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-200</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
+      <c r="T10" s="3">
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>700</v>
       </c>
       <c r="J12" s="3">
         <v>700</v>
       </c>
       <c r="K12" s="3">
+        <v>700</v>
+      </c>
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1500</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1279,8 +1299,8 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1288,21 +1308,21 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1338,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1422,14 +1445,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,163 +1496,167 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E17" s="3">
         <v>9300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,20 +1666,23 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1693,52 +1727,52 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-300</v>
       </c>
       <c r="K20" s="3">
         <v>-300</v>
       </c>
       <c r="L20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-300</v>
       </c>
       <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-200</v>
+      <c r="Q20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S20" s="3">
         <v>-200</v>
       </c>
       <c r="T20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
@@ -1746,8 +1780,8 @@
       <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>100</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1758,8 +1792,8 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
@@ -1767,77 +1801,80 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-4600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1847,20 +1884,23 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,106 +1988,112 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2761,52 +2831,52 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>300</v>
       </c>
       <c r="K32" s="3">
         <v>300</v>
       </c>
       <c r="L32" s="3">
+        <v>300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>300</v>
       </c>
       <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3">
-        <v>200</v>
+      <c r="Q32" s="3">
+        <v>300</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S32" s="3">
         <v>200</v>
       </c>
       <c r="T32" s="3">
+        <v>200</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
@@ -2814,8 +2884,8 @@
       <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>-100</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2826,8 +2896,8 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
@@ -2835,100 +2905,106 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,86 +3351,87 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E41" s="3">
         <v>21400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>21300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,65 +3533,68 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>800</v>
       </c>
       <c r="K43" s="3">
         <v>800</v>
       </c>
       <c r="L43" s="3">
+        <v>800</v>
+      </c>
+      <c r="M43" s="3">
         <v>5500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
-      </c>
-      <c r="N43" s="3">
-        <v>300</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3514,8 +3607,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3532,28 +3625,31 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>600</v>
-      </c>
-      <c r="I44" s="3">
-        <v>500</v>
       </c>
       <c r="J44" s="3">
         <v>500</v>
@@ -3562,22 +3658,22 @@
         <v>500</v>
       </c>
       <c r="L44" s="3">
+        <v>500</v>
+      </c>
+      <c r="M44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>1700</v>
       </c>
       <c r="R44" s="3">
         <v>1700</v>
@@ -3586,11 +3682,11 @@
         <v>1700</v>
       </c>
       <c r="T44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U44" s="3">
         <v>400</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3603,8 +3699,8 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,77 +3729,77 @@
         <v>1100</v>
       </c>
       <c r="E45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>800</v>
       </c>
       <c r="R45" s="3">
         <v>800</v>
       </c>
       <c r="S45" s="3">
+        <v>800</v>
+      </c>
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>800</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>200</v>
       </c>
       <c r="Z45" s="3">
         <v>200</v>
       </c>
       <c r="AA45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,86 +3809,89 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E46" s="3">
         <v>26800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>27500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11400</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,31 +3993,34 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
       </c>
       <c r="H48" s="3">
+        <v>200</v>
+      </c>
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
@@ -3921,7 +4029,7 @@
         <v>200</v>
       </c>
       <c r="M48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
@@ -3930,22 +4038,22 @@
         <v>300</v>
       </c>
       <c r="P48" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1400</v>
       </c>
       <c r="V48" s="3">
         <v>1400</v>
@@ -3954,19 +4062,19 @@
         <v>1400</v>
       </c>
       <c r="X48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y48" s="3">
         <v>800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>200</v>
       </c>
       <c r="AA48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>200</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -3977,40 +4085,43 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E49" s="3">
         <v>4700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>500</v>
       </c>
       <c r="N49" s="3">
         <v>500</v>
@@ -4019,13 +4130,13 @@
         <v>500</v>
       </c>
       <c r="P49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>600</v>
       </c>
       <c r="R49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S49" s="3">
         <v>700</v>
@@ -4033,8 +4144,8 @@
       <c r="T49" s="3">
         <v>700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>700</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -4048,8 +4159,8 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4289,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -4301,7 +4421,7 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4310,20 +4430,20 @@
         <v>0</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,86 +4545,89 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E54" s="3">
         <v>31700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,86 +4707,87 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,58 +4797,61 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5400</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1500</v>
       </c>
       <c r="F58" s="3">
         <v>1500</v>
       </c>
       <c r="G58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>700</v>
       </c>
       <c r="O58" s="3">
         <v>700</v>
       </c>
       <c r="P58" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>200</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>200</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -4734,8 +4868,8 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4755,86 +4889,89 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1400</v>
       </c>
       <c r="L59" s="3">
         <v>1400</v>
       </c>
       <c r="M59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>600</v>
       </c>
       <c r="V59" s="3">
         <v>600</v>
       </c>
       <c r="W59" s="3">
+        <v>600</v>
+      </c>
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4844,86 +4981,89 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E60" s="3">
         <v>16200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4942,56 +5085,56 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>4200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6400</v>
-      </c>
-      <c r="P61" s="3">
-        <v>6800</v>
       </c>
       <c r="Q61" s="3">
         <v>6800</v>
       </c>
       <c r="R61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="S61" s="3">
         <v>4800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5034,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
@@ -5043,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -5058,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -5067,19 +5213,19 @@
         <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -5088,20 +5234,20 @@
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>1600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>600</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,31 +5533,34 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E66" s="3">
         <v>16300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>9800</v>
       </c>
       <c r="K66" s="3">
         <v>9800</v>
@@ -5411,53 +5569,53 @@
         <v>9800</v>
       </c>
       <c r="M66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="N66" s="3">
         <v>10900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5747,17 +5915,17 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>21200</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>20400</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>19700</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,86 +6027,89 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-104100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-101800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-101200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-105800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-103100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-104000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-101000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-99400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-94100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-95200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-89100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-87000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-92200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-84500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-78000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-73200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-64200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-61500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-56500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-53300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-45900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-19800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,8 +6395,11 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6221,77 +6407,77 @@
         <v>15500</v>
       </c>
       <c r="E76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F76" s="3">
         <v>16900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7000</v>
-      </c>
-      <c r="S76" s="3">
-        <v>10600</v>
       </c>
       <c r="T76" s="3">
         <v>10600</v>
       </c>
       <c r="U76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="V76" s="3">
         <v>12300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6615,7 +6814,7 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -6624,19 +6823,19 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -6645,7 +6844,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -6660,7 +6859,7 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6672,7 +6871,7 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -6692,11 +6891,14 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,17 +7482,18 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -7283,28 +7504,28 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7322,22 +7543,22 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-100</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
@@ -7346,13 +7567,16 @@
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,17 +7756,20 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -7550,26 +7780,26 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-3300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>700</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -7583,28 +7813,28 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-100</v>
       </c>
       <c r="Y94" s="3">
         <v>-100</v>
       </c>
       <c r="Z94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
@@ -7613,13 +7843,16 @@
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,77 +8250,80 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>22000</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8085,19 +8331,22 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>18000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>18000</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="S102" s="3">
-        <v>300</v>
       </c>
       <c r="T102" s="3">
         <v>300</v>
       </c>
       <c r="U102" s="3">
+        <v>300</v>
+      </c>
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20100</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-2300</v>
       </c>
       <c r="Z102" s="3">
         <v>-2300</v>
       </c>
       <c r="AA102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16600</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,209 +656,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E8" s="3">
         <v>8000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>500</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,8 +872,8 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -880,65 +884,68 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E9" s="3">
         <v>3000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-100</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
       <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,64 +979,67 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-200</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0</v>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T10" s="3">
         <v>0</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
+      <c r="U10" s="3">
+        <v>0</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>700</v>
       </c>
       <c r="K12" s="3">
         <v>700</v>
       </c>
       <c r="L12" s="3">
+        <v>700</v>
+      </c>
+      <c r="M12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1500</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1302,8 +1322,8 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1311,21 +1331,21 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1361,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1448,14 +1471,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,169 +1523,173 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2200</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-4600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,20 +1699,23 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,13 +1748,14 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1730,52 +1764,52 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-300</v>
       </c>
       <c r="L20" s="3">
         <v>-300</v>
       </c>
       <c r="M20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-300</v>
       </c>
       <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
+      <c r="R20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T20" s="3">
         <v>-200</v>
       </c>
       <c r="U20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
@@ -1783,8 +1817,8 @@
       <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>100</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1795,8 +1829,8 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -1804,80 +1838,83 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-4600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1887,20 +1924,23 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,112 +2031,118 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,13 +2886,16 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2834,52 +2904,52 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>300</v>
       </c>
       <c r="L32" s="3">
         <v>300</v>
       </c>
       <c r="M32" s="3">
+        <v>300</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>300</v>
       </c>
       <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
+      <c r="R32" s="3">
+        <v>300</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T32" s="3">
         <v>200</v>
       </c>
       <c r="U32" s="3">
+        <v>200</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
@@ -2887,8 +2957,8 @@
       <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>-100</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2899,8 +2969,8 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -2908,103 +2978,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,89 +3438,90 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E41" s="3">
         <v>16700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3531,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,68 +3626,71 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E43" s="3">
         <v>4200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>800</v>
       </c>
       <c r="L43" s="3">
         <v>800</v>
       </c>
       <c r="M43" s="3">
+        <v>800</v>
+      </c>
+      <c r="N43" s="3">
         <v>5500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>300</v>
       </c>
       <c r="P43" s="3">
         <v>300</v>
       </c>
       <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3703,8 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3628,31 +3721,34 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
-      </c>
-      <c r="J44" s="3">
-        <v>500</v>
       </c>
       <c r="K44" s="3">
         <v>500</v>
@@ -3661,22 +3757,22 @@
         <v>500</v>
       </c>
       <c r="M44" s="3">
+        <v>500</v>
+      </c>
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1200</v>
-      </c>
-      <c r="R44" s="3">
-        <v>1700</v>
       </c>
       <c r="S44" s="3">
         <v>1700</v>
@@ -3685,11 +3781,11 @@
         <v>1700</v>
       </c>
       <c r="U44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V44" s="3">
         <v>400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,8 +3798,8 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
@@ -3720,89 +3816,92 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
         <v>1100</v>
       </c>
       <c r="F45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>800</v>
       </c>
       <c r="S45" s="3">
         <v>800</v>
       </c>
       <c r="T45" s="3">
+        <v>800</v>
+      </c>
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>200</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
       </c>
       <c r="AB45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,89 +3911,92 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E46" s="3">
         <v>24300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11400</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,34 +4101,37 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
       </c>
       <c r="I48" s="3">
+        <v>200</v>
+      </c>
+      <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
@@ -4032,7 +4140,7 @@
         <v>200</v>
       </c>
       <c r="N48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -4041,22 +4149,22 @@
         <v>300</v>
       </c>
       <c r="Q48" s="3">
+        <v>300</v>
+      </c>
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1400</v>
       </c>
       <c r="W48" s="3">
         <v>1400</v>
@@ -4065,19 +4173,19 @@
         <v>1400</v>
       </c>
       <c r="Y48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z48" s="3">
         <v>800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>300</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>200</v>
       </c>
       <c r="AB48" s="3">
         <v>200</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
+      <c r="AC48" s="3">
+        <v>200</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
@@ -4088,43 +4196,46 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E49" s="3">
         <v>6400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>500</v>
       </c>
       <c r="O49" s="3">
         <v>500</v>
@@ -4133,13 +4244,13 @@
         <v>500</v>
       </c>
       <c r="Q49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>600</v>
       </c>
       <c r="S49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T49" s="3">
         <v>700</v>
@@ -4147,8 +4258,8 @@
       <c r="U49" s="3">
         <v>700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>700</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -4162,8 +4273,8 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4412,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -4424,7 +4544,7 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4433,20 +4553,20 @@
         <v>0</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>200</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,89 +4671,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E54" s="3">
         <v>30800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11700</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,89 +4838,90 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,61 +4931,64 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
         <v>5000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1500</v>
       </c>
       <c r="G58" s="3">
         <v>1500</v>
       </c>
       <c r="H58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1100</v>
-      </c>
-      <c r="O58" s="3">
-        <v>700</v>
       </c>
       <c r="P58" s="3">
         <v>700</v>
       </c>
       <c r="Q58" s="3">
+        <v>700</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
-      </c>
-      <c r="R58" s="3">
-        <v>200</v>
       </c>
       <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>200</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4871,8 +5005,8 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4892,89 +5026,92 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E59" s="3">
         <v>8000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1400</v>
       </c>
       <c r="M59" s="3">
         <v>1400</v>
       </c>
       <c r="N59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>600</v>
       </c>
       <c r="W59" s="3">
         <v>600</v>
       </c>
       <c r="X59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,89 +5121,92 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E60" s="3">
         <v>15300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>900</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5088,56 +5231,56 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>4200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6400</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>6800</v>
       </c>
       <c r="R61" s="3">
         <v>6800</v>
       </c>
       <c r="S61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T61" s="3">
         <v>4800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -5168,13 +5311,16 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -5183,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
@@ -5192,7 +5338,7 @@
         <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5207,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -5216,19 +5362,19 @@
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -5237,20 +5383,20 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>600</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,34 +5691,37 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E66" s="3">
         <v>15300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>9800</v>
       </c>
       <c r="L66" s="3">
         <v>9800</v>
@@ -5572,53 +5730,53 @@
         <v>9800</v>
       </c>
       <c r="N66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O66" s="3">
         <v>10900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1600</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,17 +6086,17 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>21200</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>20400</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>19700</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,89 +6201,92 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-107900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-104900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-104100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-101800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-101200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-105800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-103100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-104000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-101000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-99400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-94100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-95200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-89100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-87000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-92200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-84500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-78000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-73200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-64200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-61500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-56500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-53300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-45900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-19800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,89 +6581,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15500</v>
+        <v>13500</v>
       </c>
       <c r="E76" s="3">
         <v>15500</v>
       </c>
       <c r="F76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G76" s="3">
         <v>16900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7000</v>
-      </c>
-      <c r="T76" s="3">
-        <v>10600</v>
       </c>
       <c r="U76" s="3">
         <v>10600</v>
       </c>
       <c r="V76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="W76" s="3">
         <v>12300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>26300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6817,7 +7016,7 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -6826,19 +7025,19 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -6847,7 +7046,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -6862,7 +7061,7 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -6874,7 +7073,7 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6894,11 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,20 +7703,21 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -7507,28 +7728,28 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7546,22 +7767,22 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
@@ -7570,13 +7791,16 @@
         <v>-100</v>
       </c>
       <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,20 +7986,23 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -7783,26 +8013,26 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-3300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>700</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -7816,28 +8046,28 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
@@ -7846,13 +8076,16 @@
         <v>-100</v>
       </c>
       <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,80 +8496,83 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>7500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>22000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8334,19 +8580,22 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>18000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>18000</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="T102" s="3">
-        <v>300</v>
       </c>
       <c r="U102" s="3">
         <v>300</v>
       </c>
       <c r="V102" s="3">
+        <v>300</v>
+      </c>
+      <c r="W102" s="3">
         <v>-3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20100</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-2300</v>
       </c>
       <c r="AA102" s="3">
         <v>-2300</v>
       </c>
       <c r="AB102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16600</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,216 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E8" s="3">
         <v>9100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>500</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,8 +879,8 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE8" s="3">
         <v>0</v>
@@ -887,68 +891,71 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-100</v>
       </c>
-      <c r="T9" s="3">
-        <v>0</v>
-      </c>
       <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -982,67 +989,70 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K10" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O10" s="3">
         <v>5700</v>
       </c>
-      <c r="E10" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>6400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>4700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N10" s="3">
-        <v>5700</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-200</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0</v>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
+      <c r="V10" s="3">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,103 +1125,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>700</v>
       </c>
       <c r="L12" s="3">
         <v>700</v>
       </c>
       <c r="M12" s="3">
+        <v>700</v>
+      </c>
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1500</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1325,8 +1345,8 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1334,21 +1354,21 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1364,8 +1384,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1397,31 +1417,34 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1474,14 +1497,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,175 +1550,179 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E17" s="3">
         <v>12000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2200</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
         <v>3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-4600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1702,20 +1732,23 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,70 +1782,71 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>800</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-300</v>
       </c>
       <c r="M20" s="3">
         <v>-300</v>
       </c>
       <c r="N20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-300</v>
       </c>
       <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-200</v>
+      <c r="S20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U20" s="3">
         <v>-200</v>
       </c>
       <c r="V20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
@@ -1820,8 +1854,8 @@
       <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>100</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1832,8 +1866,8 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
@@ -1841,83 +1875,86 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1700</v>
-      </c>
       <c r="G21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H21" s="3">
         <v>-400</v>
       </c>
-      <c r="H21" s="3">
-        <v>4800</v>
-      </c>
       <c r="I21" s="3">
-        <v>-2400</v>
+        <v>4900</v>
       </c>
       <c r="J21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-4600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,43 +1964,46 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2034,126 +2074,132 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,70 +2956,73 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>800</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>200</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>300</v>
       </c>
       <c r="M32" s="3">
         <v>300</v>
       </c>
       <c r="N32" s="3">
+        <v>300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>300</v>
       </c>
       <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3">
-        <v>200</v>
+      <c r="S32" s="3">
+        <v>300</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U32" s="3">
         <v>200</v>
       </c>
       <c r="V32" s="3">
+        <v>200</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
@@ -2960,8 +3030,8 @@
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>-100</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2972,8 +3042,8 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
@@ -2981,106 +3051,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,92 +3525,93 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E41" s="3">
         <v>17700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>26700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,71 +3719,74 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E43" s="3">
         <v>4900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>800</v>
       </c>
       <c r="M43" s="3">
         <v>800</v>
       </c>
       <c r="N43" s="3">
+        <v>800</v>
+      </c>
+      <c r="O43" s="3">
         <v>5500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
       </c>
       <c r="Q43" s="3">
         <v>300</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3706,8 +3799,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3724,34 +3817,37 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>600</v>
-      </c>
-      <c r="K44" s="3">
-        <v>500</v>
       </c>
       <c r="L44" s="3">
         <v>500</v>
@@ -3760,22 +3856,22 @@
         <v>500</v>
       </c>
       <c r="N44" s="3">
+        <v>500</v>
+      </c>
+      <c r="O44" s="3">
         <v>600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1200</v>
-      </c>
-      <c r="S44" s="3">
-        <v>1700</v>
       </c>
       <c r="T44" s="3">
         <v>1700</v>
@@ -3784,11 +3880,11 @@
         <v>1700</v>
       </c>
       <c r="V44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W44" s="3">
         <v>400</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,8 +3897,8 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
@@ -3819,92 +3915,95 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>800</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>800</v>
       </c>
       <c r="T45" s="3">
         <v>800</v>
       </c>
       <c r="U45" s="3">
+        <v>800</v>
+      </c>
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>200</v>
       </c>
       <c r="AB45" s="3">
         <v>200</v>
       </c>
       <c r="AC45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3914,92 +4013,95 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E46" s="3">
         <v>25400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>11400</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4009,31 +4111,34 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4104,37 +4209,40 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>200</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
       </c>
       <c r="J48" s="3">
+        <v>200</v>
+      </c>
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -4143,7 +4251,7 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
@@ -4152,22 +4260,22 @@
         <v>300</v>
       </c>
       <c r="R48" s="3">
+        <v>300</v>
+      </c>
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1300</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1400</v>
       </c>
       <c r="X48" s="3">
         <v>1400</v>
@@ -4176,19 +4284,19 @@
         <v>1400</v>
       </c>
       <c r="Z48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA48" s="3">
         <v>800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>200</v>
       </c>
       <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
+      <c r="AD48" s="3">
+        <v>200</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
@@ -4199,46 +4307,49 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E49" s="3">
         <v>6100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>500</v>
@@ -4247,13 +4358,13 @@
         <v>500</v>
       </c>
       <c r="R49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>600</v>
       </c>
       <c r="T49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U49" s="3">
         <v>700</v>
@@ -4261,8 +4372,8 @@
       <c r="V49" s="3">
         <v>700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>700</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -4276,8 +4387,8 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4535,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4547,7 +4667,7 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4556,20 +4676,20 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>200</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,92 +4797,95 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E54" s="3">
         <v>31800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,92 +4969,93 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,64 +5065,67 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>4700</v>
       </c>
-      <c r="E58" s="3">
-        <v>5000</v>
-      </c>
       <c r="F58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G58" s="3">
         <v>5400</v>
       </c>
-      <c r="G58" s="3">
-        <v>1500</v>
-      </c>
       <c r="H58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I58" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="J58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>1400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1100</v>
-      </c>
-      <c r="P58" s="3">
-        <v>700</v>
       </c>
       <c r="Q58" s="3">
         <v>700</v>
       </c>
       <c r="R58" s="3">
+        <v>700</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>200</v>
       </c>
       <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>200</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -5008,8 +5142,8 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5029,92 +5163,95 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>11400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>8000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>9000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>3700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1400</v>
       </c>
       <c r="N59" s="3">
         <v>1400</v>
       </c>
       <c r="O59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
-      </c>
-      <c r="W59" s="3">
-        <v>600</v>
       </c>
       <c r="X59" s="3">
         <v>600</v>
       </c>
       <c r="Y59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>100</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5124,92 +5261,95 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E60" s="3">
         <v>18200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5219,71 +5359,74 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>4200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4600</v>
       </c>
-      <c r="I61" s="3">
-        <v>5100</v>
-      </c>
       <c r="J61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K61" s="3">
         <v>5400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6400</v>
-      </c>
-      <c r="R61" s="3">
-        <v>6800</v>
       </c>
       <c r="S61" s="3">
         <v>6800</v>
       </c>
       <c r="T61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="U61" s="3">
         <v>4800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5314,35 +5457,38 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5356,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -5365,19 +5511,19 @@
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X62" s="3">
         <v>100</v>
@@ -5386,20 +5532,20 @@
         <v>100</v>
       </c>
       <c r="Z62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>600</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,37 +5849,40 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E66" s="3">
         <v>18400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>9800</v>
       </c>
       <c r="M66" s="3">
         <v>9800</v>
@@ -5733,53 +5891,53 @@
         <v>9800</v>
       </c>
       <c r="O66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P66" s="3">
         <v>10900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1600</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6089,17 +6257,17 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>21200</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>20400</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>19700</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,92 +6375,95 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-107900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-104900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-104100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-101800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-101200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-105800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-103100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-104000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-101000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-99400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-94100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-95200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-89100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-87000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-92200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-84500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-78000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-73200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-64200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-61500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-56500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-53300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-45900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,92 +6767,95 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13500</v>
-      </c>
-      <c r="E76" s="3">
-        <v>15500</v>
       </c>
       <c r="F76" s="3">
         <v>15500</v>
       </c>
       <c r="G76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="H76" s="3">
         <v>16900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7000</v>
-      </c>
-      <c r="U76" s="3">
-        <v>10600</v>
       </c>
       <c r="V76" s="3">
         <v>10600</v>
       </c>
       <c r="W76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="X76" s="3">
         <v>12300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>26300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,43 +7202,44 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>300</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -7049,7 +7248,7 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -7064,7 +7263,7 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -7076,7 +7275,7 @@
         <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -7096,11 +7295,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7713,46 +7934,46 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7770,22 +7991,22 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
@@ -7794,13 +8015,16 @@
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7998,44 +8228,44 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>700</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8049,28 +8279,28 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
       </c>
       <c r="AB94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
@@ -8079,13 +8309,16 @@
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,31 +8352,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,83 +8742,86 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>21200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>22000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -8583,42 +8829,45 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>18000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>18000</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="U102" s="3">
-        <v>300</v>
       </c>
       <c r="V102" s="3">
         <v>300</v>
       </c>
       <c r="W102" s="3">
+        <v>300</v>
+      </c>
+      <c r="X102" s="3">
         <v>-3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>20100</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-2300</v>
       </c>
       <c r="AB102" s="3">
         <v>-2300</v>
       </c>
       <c r="AC102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>16600</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,223 +656,226 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E8" s="3">
         <v>10300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>500</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,8 +885,8 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF8" s="3">
         <v>0</v>
@@ -894,71 +897,74 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E9" s="3">
         <v>4000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-100</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
       <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -992,70 +998,73 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E10" s="3">
         <v>6300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>700</v>
       </c>
       <c r="M12" s="3">
         <v>700</v>
       </c>
       <c r="N12" s="3">
+        <v>700</v>
+      </c>
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1500</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1348,8 +1367,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1357,21 +1376,21 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1420,25 +1439,28 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
       </c>
       <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
         <v>200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
@@ -1447,7 +1469,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1500,14 +1522,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,181 +1576,185 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2200</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>600</v>
+      </c>
+      <c r="E18" s="3">
         <v>500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-4600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,20 +1764,23 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1797,59 +1830,59 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-300</v>
       </c>
       <c r="N20" s="3">
         <v>-300</v>
       </c>
       <c r="O20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-300</v>
       </c>
       <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-200</v>
+      <c r="T20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V20" s="3">
         <v>-200</v>
       </c>
       <c r="W20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
@@ -1857,8 +1890,8 @@
       <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>100</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
@@ -1869,8 +1902,8 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
@@ -1878,86 +1911,89 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-4600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1967,47 +2003,50 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2077,132 +2116,138 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2273,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2973,59 +3042,59 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>300</v>
       </c>
       <c r="N32" s="3">
         <v>300</v>
       </c>
       <c r="O32" s="3">
+        <v>300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>300</v>
       </c>
       <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3">
-        <v>200</v>
+      <c r="T32" s="3">
+        <v>300</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V32" s="3">
         <v>200</v>
       </c>
       <c r="W32" s="3">
+        <v>200</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
@@ -3033,8 +3102,8 @@
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>-100</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
@@ -3045,8 +3114,8 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
@@ -3054,109 +3123,115 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,95 +3611,96 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E41" s="3">
         <v>20300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>25100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>26700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,8 +3710,11 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,74 +3811,77 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E43" s="3">
         <v>5600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>800</v>
       </c>
       <c r="N43" s="3">
         <v>800</v>
       </c>
       <c r="O43" s="3">
+        <v>800</v>
+      </c>
+      <c r="P43" s="3">
         <v>5500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>300</v>
       </c>
       <c r="R43" s="3">
         <v>300</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +3894,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3820,37 +3912,40 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
-      </c>
-      <c r="L44" s="3">
-        <v>500</v>
       </c>
       <c r="M44" s="3">
         <v>500</v>
@@ -3859,22 +3954,22 @@
         <v>500</v>
       </c>
       <c r="O44" s="3">
+        <v>500</v>
+      </c>
+      <c r="P44" s="3">
         <v>600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1200</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1700</v>
       </c>
       <c r="U44" s="3">
         <v>1700</v>
@@ -3883,11 +3978,11 @@
         <v>1700</v>
       </c>
       <c r="W44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X44" s="3">
         <v>400</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3900,8 +3995,8 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -3918,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3944,69 +4042,69 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>800</v>
       </c>
       <c r="U45" s="3">
         <v>800</v>
       </c>
       <c r="V45" s="3">
+        <v>800</v>
+      </c>
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>200</v>
       </c>
       <c r="AC45" s="3">
         <v>200</v>
       </c>
       <c r="AD45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4016,95 +4114,98 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E46" s="3">
         <v>29700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>21500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11400</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4114,8 +4215,11 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4140,8 +4244,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4212,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4221,31 +4328,31 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
       </c>
       <c r="K48" s="3">
+        <v>200</v>
+      </c>
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
@@ -4254,7 +4361,7 @@
         <v>200</v>
       </c>
       <c r="P48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>300</v>
@@ -4263,22 +4370,22 @@
         <v>300</v>
       </c>
       <c r="S48" s="3">
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1400</v>
       </c>
       <c r="Y48" s="3">
         <v>1400</v>
@@ -4287,19 +4394,19 @@
         <v>1400</v>
       </c>
       <c r="AA48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB48" s="3">
         <v>800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>300</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>200</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AE48" s="3">
+        <v>200</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
@@ -4310,49 +4417,52 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3600</v>
-      </c>
-      <c r="P49" s="3">
-        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>500</v>
@@ -4361,13 +4471,13 @@
         <v>500</v>
       </c>
       <c r="S49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>600</v>
       </c>
       <c r="U49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V49" s="3">
         <v>700</v>
@@ -4375,8 +4485,8 @@
       <c r="W49" s="3">
         <v>700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>700</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -4390,8 +4500,8 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4658,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4670,7 +4789,7 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4679,20 +4798,20 @@
         <v>0</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>200</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,95 +4922,98 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E54" s="3">
         <v>35800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4898,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,95 +5099,96 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>800</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5068,67 +5198,70 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>4200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1600</v>
       </c>
       <c r="I58" s="3">
         <v>1600</v>
       </c>
       <c r="J58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>700</v>
       </c>
       <c r="R58" s="3">
         <v>700</v>
       </c>
       <c r="S58" s="3">
+        <v>700</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
-      </c>
-      <c r="T58" s="3">
-        <v>200</v>
       </c>
       <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>200</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -5145,8 +5278,8 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5166,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5192,69 +5328,69 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>3700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2100</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1400</v>
       </c>
       <c r="O59" s="3">
         <v>1400</v>
       </c>
       <c r="P59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1400</v>
-      </c>
-      <c r="X59" s="3">
-        <v>600</v>
       </c>
       <c r="Y59" s="3">
         <v>600</v>
       </c>
       <c r="Z59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5264,95 +5400,98 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E60" s="3">
         <v>19700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5362,74 +5501,77 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>29900</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>4200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6400</v>
-      </c>
-      <c r="S61" s="3">
-        <v>6800</v>
       </c>
       <c r="T61" s="3">
         <v>6800</v>
       </c>
       <c r="U61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="V61" s="3">
         <v>4800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5460,13 +5602,16 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>1800</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
@@ -5486,12 +5631,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5505,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -5514,19 +5659,19 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="3">
         <v>100</v>
@@ -5535,20 +5680,20 @@
         <v>100</v>
       </c>
       <c r="AA62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
         <v>1600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>600</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5558,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,40 +6006,43 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E66" s="3">
         <v>19900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10300</v>
-      </c>
-      <c r="M66" s="3">
-        <v>9800</v>
       </c>
       <c r="N66" s="3">
         <v>9800</v>
@@ -5894,53 +6051,53 @@
         <v>9800</v>
       </c>
       <c r="P66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Q66" s="3">
         <v>10900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1600</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5950,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6260,17 +6427,17 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>21200</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>20400</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>19700</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,95 +6548,98 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-107900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-107300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-107900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-104900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-104100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-101800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-101200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-105800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-103100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-104000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-101000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-99400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-94100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-95200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-89100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-87000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-92200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-84500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-78000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-73200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-64200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-61500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-56500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-53300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-45900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-19800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6476,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,95 +6952,98 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E76" s="3">
         <v>16000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13500</v>
-      </c>
-      <c r="F76" s="3">
-        <v>15500</v>
       </c>
       <c r="G76" s="3">
         <v>15500</v>
       </c>
       <c r="H76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I76" s="3">
         <v>16900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7000</v>
-      </c>
-      <c r="V76" s="3">
-        <v>10600</v>
       </c>
       <c r="W76" s="3">
         <v>10600</v>
       </c>
       <c r="X76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="Y76" s="3">
         <v>12300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6868,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,46 +7400,47 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -7251,7 +7449,7 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -7266,7 +7464,7 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
@@ -7278,7 +7476,7 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -7298,11 +7496,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7939,8 +8159,8 @@
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -7951,32 +8171,32 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -7994,22 +8214,22 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-100</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
@@ -8018,13 +8238,16 @@
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,56 +8445,59 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-38100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>700</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -8282,28 +8511,28 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-100</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
@@ -8312,13 +8541,16 @@
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8379,8 +8612,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,86 +8987,89 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>21200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>22000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
@@ -8832,19 +9077,22 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>18000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>18000</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8869,8 +9117,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8941,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="V102" s="3">
-        <v>300</v>
       </c>
       <c r="W102" s="3">
         <v>300</v>
       </c>
       <c r="X102" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20100</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>-2300</v>
       </c>
       <c r="AC102" s="3">
         <v>-2300</v>
       </c>
       <c r="AD102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>16600</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,229 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E8" s="3">
         <v>11600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>500</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
       <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
         <v>500</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,8 +892,8 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF8" s="3">
-        <v>0</v>
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG8" s="3">
         <v>0</v>
@@ -900,74 +904,77 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E9" s="3">
         <v>5200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-100</v>
       </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
       <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,73 +1008,76 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E10" s="3">
         <v>6500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0</v>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
+      <c r="X10" s="3">
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
         <v>-900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>700</v>
       </c>
       <c r="N12" s="3">
         <v>700</v>
       </c>
       <c r="O12" s="3">
+        <v>700</v>
+      </c>
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1500</v>
       </c>
-      <c r="AI12" s="3" t="s">
+      <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,16 +1358,19 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1370,8 +1390,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1379,21 +1399,21 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1409,8 +1429,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1442,13 +1462,16 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1457,13 +1480,13 @@
         <v>300</v>
       </c>
       <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
@@ -1472,7 +1495,7 @@
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1525,14 +1548,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,187 +1603,191 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11000</v>
+        <v>17800</v>
       </c>
       <c r="E17" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F17" s="3">
         <v>9800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2200</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>600</v>
+        <v>-500</v>
       </c>
       <c r="E18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-4600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,20 +1797,23 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1833,59 +1867,59 @@
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-300</v>
       </c>
       <c r="O20" s="3">
         <v>-300</v>
       </c>
       <c r="P20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-300</v>
       </c>
       <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-200</v>
+      <c r="U20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W20" s="3">
         <v>-200</v>
       </c>
       <c r="X20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
@@ -1893,8 +1927,8 @@
       <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>100</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1905,8 +1939,8 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
@@ -1914,89 +1948,92 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-4600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,50 +2043,53 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2119,109 +2159,115 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2229,28 +2275,28 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3045,59 +3115,59 @@
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>300</v>
       </c>
       <c r="O32" s="3">
         <v>300</v>
       </c>
       <c r="P32" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>300</v>
       </c>
       <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3">
-        <v>200</v>
+      <c r="U32" s="3">
+        <v>300</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W32" s="3">
         <v>200</v>
       </c>
       <c r="X32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
@@ -3105,8 +3175,8 @@
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>-100</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -3117,8 +3187,8 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
@@ -3126,112 +3196,118 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,98 +3698,99 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E41" s="3">
         <v>14900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>25800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>14900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>19600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>26700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11200</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3713,8 +3800,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,77 +3904,80 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E43" s="3">
         <v>5400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>800</v>
       </c>
       <c r="O43" s="3">
         <v>800</v>
       </c>
       <c r="P43" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q43" s="3">
         <v>5500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
-      </c>
-      <c r="R43" s="3">
-        <v>300</v>
       </c>
       <c r="S43" s="3">
         <v>300</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3897,8 +3990,8 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -3915,40 +4008,43 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E44" s="3">
         <v>15200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>600</v>
-      </c>
-      <c r="M44" s="3">
-        <v>500</v>
       </c>
       <c r="N44" s="3">
         <v>500</v>
@@ -3957,22 +4053,22 @@
         <v>500</v>
       </c>
       <c r="P44" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1200</v>
-      </c>
-      <c r="U44" s="3">
-        <v>1700</v>
       </c>
       <c r="V44" s="3">
         <v>1700</v>
@@ -3981,11 +4077,11 @@
         <v>1700</v>
       </c>
       <c r="X44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y44" s="3">
         <v>400</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4094,8 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
@@ -4016,8 +4112,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4045,69 +4144,69 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
-      </c>
-      <c r="U45" s="3">
-        <v>800</v>
       </c>
       <c r="V45" s="3">
         <v>800</v>
       </c>
       <c r="W45" s="3">
+        <v>800</v>
+      </c>
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>200</v>
       </c>
       <c r="AD45" s="3">
         <v>200</v>
       </c>
       <c r="AE45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4117,98 +4216,101 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E46" s="3">
         <v>41000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>30300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>21500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11400</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4320,11 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4247,8 +4352,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4331,31 +4439,31 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
+        <v>200</v>
+      </c>
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
+        <v>200</v>
+      </c>
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
@@ -4364,7 +4472,7 @@
         <v>200</v>
       </c>
       <c r="Q48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
@@ -4373,22 +4481,22 @@
         <v>300</v>
       </c>
       <c r="T48" s="3">
+        <v>300</v>
+      </c>
+      <c r="U48" s="3">
         <v>1000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1400</v>
       </c>
       <c r="Z48" s="3">
         <v>1400</v>
@@ -4397,19 +4505,19 @@
         <v>1400</v>
       </c>
       <c r="AB48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC48" s="3">
         <v>800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>300</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>200</v>
       </c>
       <c r="AE48" s="3">
         <v>200</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
+      <c r="AF48" s="3">
+        <v>200</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
@@ -4420,52 +4528,55 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E49" s="3">
         <v>34900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>500</v>
@@ -4474,13 +4585,13 @@
         <v>500</v>
       </c>
       <c r="T49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U49" s="3">
         <v>600</v>
       </c>
       <c r="V49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W49" s="3">
         <v>700</v>
@@ -4488,8 +4599,8 @@
       <c r="X49" s="3">
         <v>700</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>700</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
@@ -4503,8 +4614,8 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4780,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -4792,7 +4912,7 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4801,20 +4921,20 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
         <v>100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>200</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,98 +5048,101 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E54" s="3">
         <v>76100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>35800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,98 +5230,99 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>800</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5201,8 +5332,11 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,61 +5344,61 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
         <v>4200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1600</v>
       </c>
       <c r="J58" s="3">
         <v>1600</v>
       </c>
       <c r="K58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>700</v>
       </c>
       <c r="S58" s="3">
         <v>700</v>
       </c>
       <c r="T58" s="3">
+        <v>700</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
-      </c>
-      <c r="U58" s="3">
-        <v>200</v>
       </c>
       <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>200</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -5281,8 +5415,8 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5302,8 +5436,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5331,69 +5468,69 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>3700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1400</v>
       </c>
       <c r="P59" s="3">
         <v>1400</v>
       </c>
       <c r="Q59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>600</v>
       </c>
       <c r="Z59" s="3">
         <v>600</v>
       </c>
       <c r="AA59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5403,98 +5540,101 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E60" s="3">
         <v>19900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5504,77 +5644,80 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E61" s="3">
         <v>29900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>4200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6400</v>
-      </c>
-      <c r="T61" s="3">
-        <v>6800</v>
       </c>
       <c r="U61" s="3">
         <v>6800</v>
       </c>
       <c r="V61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="W61" s="3">
         <v>4800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4500</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5605,17 +5748,20 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5634,12 +5780,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -5653,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5662,19 +5808,19 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
@@ -5683,20 +5829,20 @@
         <v>100</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>600</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,43 +6164,46 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E66" s="3">
         <v>51700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10300</v>
-      </c>
-      <c r="N66" s="3">
-        <v>9800</v>
       </c>
       <c r="O66" s="3">
         <v>9800</v>
@@ -6054,53 +6212,53 @@
         <v>9800</v>
       </c>
       <c r="Q66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="R66" s="3">
         <v>10900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1600</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6430,17 +6598,17 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>21200</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>20400</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>19700</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,98 +6722,101 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-109500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-107900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-107300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-107900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-104900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-104100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-101800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-101200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-105800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-103100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-104000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-101000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-99400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-94100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-95200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-89100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-87000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-92200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-84500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-78000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-73200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-64200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-53300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-45900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-19800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,98 +7138,101 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E76" s="3">
         <v>24400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>15500</v>
       </c>
       <c r="H76" s="3">
         <v>15500</v>
       </c>
       <c r="I76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="J76" s="3">
         <v>16900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7000</v>
-      </c>
-      <c r="W76" s="3">
-        <v>10600</v>
       </c>
       <c r="X76" s="3">
         <v>10600</v>
       </c>
       <c r="Y76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="Z76" s="3">
         <v>12300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7410,40 +7609,40 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -7452,7 +7651,7 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -7467,7 +7666,7 @@
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -7479,7 +7678,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -7499,11 +7698,14 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,13 +8365,14 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -8162,8 +8383,8 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -8174,32 +8395,32 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8217,22 +8438,22 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
@@ -8241,13 +8462,16 @@
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI91" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,59 +8675,62 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-38100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>700</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -8514,28 +8744,28 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-800</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-100</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
@@ -8544,13 +8774,16 @@
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI94" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8615,8 +8849,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,89 +9233,92 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>33600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>22000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -9080,19 +9326,22 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>18000</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>18000</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9120,8 +9369,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="W102" s="3">
-        <v>300</v>
       </c>
       <c r="X102" s="3">
         <v>300</v>
       </c>
       <c r="Y102" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20100</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-2300</v>
       </c>
       <c r="AD102" s="3">
         <v>-2300</v>
       </c>
       <c r="AE102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>13200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16600</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,236 +656,240 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E8" s="3">
         <v>17300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>500</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
       <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>500</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
@@ -895,8 +899,8 @@
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG8" s="3">
-        <v>0</v>
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH8" s="3">
         <v>0</v>
@@ -907,77 +911,80 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E9" s="3">
         <v>7400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-100</v>
       </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
       <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,76 +1018,79 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E10" s="3">
         <v>9900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0</v>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X10" s="3">
         <v>0</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
+      <c r="Y10" s="3">
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
@@ -1115,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1166,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>-900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>700</v>
       </c>
       <c r="O12" s="3">
         <v>700</v>
       </c>
       <c r="P12" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ12" s="3" t="s">
+      <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,20 +1378,23 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,8 +1413,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1402,21 +1422,21 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1465,8 +1485,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,7 +1497,7 @@
         <v>1000</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
@@ -1483,13 +1506,13 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
@@ -1498,7 +1521,7 @@
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1551,14 +1574,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>3</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,193 +1630,197 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E17" s="3">
         <v>17800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7400</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-4600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1800,20 +1830,23 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1870,59 +1904,59 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-300</v>
       </c>
       <c r="P20" s="3">
         <v>-300</v>
       </c>
       <c r="Q20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-300</v>
       </c>
       <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-200</v>
+      <c r="V20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X20" s="3">
         <v>-200</v>
       </c>
       <c r="Y20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
@@ -1930,8 +1964,8 @@
       <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>100</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1942,8 +1976,8 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
@@ -1951,92 +1985,95 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>700</v>
+      </c>
+      <c r="E21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-4600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2046,20 +2083,23 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,16 +2107,16 @@
         <v>1000</v>
       </c>
       <c r="E22" s="3">
+        <v>900</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
@@ -2085,14 +2125,14 @@
         <v>200</v>
       </c>
       <c r="K22" s="3">
+        <v>200</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2162,112 +2202,118 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ23" s="3" t="s">
+      <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2278,28 +2324,28 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2370,8 +2416,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3118,59 +3188,59 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>300</v>
       </c>
       <c r="P32" s="3">
         <v>300</v>
       </c>
       <c r="Q32" s="3">
+        <v>300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>300</v>
       </c>
       <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
-        <v>200</v>
+      <c r="V32" s="3">
+        <v>300</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X32" s="3">
         <v>200</v>
       </c>
       <c r="Y32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
@@ -3178,8 +3248,8 @@
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>-100</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -3190,8 +3260,8 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
@@ -3199,115 +3269,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2" t="s">
+      <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,101 +3785,102 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E41" s="3">
         <v>17400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>14900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>19600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11200</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +3890,11 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,80 +3997,83 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E43" s="3">
         <v>16400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1500</v>
-      </c>
-      <c r="O43" s="3">
-        <v>800</v>
       </c>
       <c r="P43" s="3">
         <v>800</v>
       </c>
       <c r="Q43" s="3">
+        <v>800</v>
+      </c>
+      <c r="R43" s="3">
         <v>5500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
-      </c>
-      <c r="S43" s="3">
-        <v>300</v>
       </c>
       <c r="T43" s="3">
         <v>300</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4086,8 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -4011,43 +4104,46 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E44" s="3">
         <v>13600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>600</v>
-      </c>
-      <c r="N44" s="3">
-        <v>500</v>
       </c>
       <c r="O44" s="3">
         <v>500</v>
@@ -4056,22 +4152,22 @@
         <v>500</v>
       </c>
       <c r="Q44" s="3">
+        <v>500</v>
+      </c>
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1200</v>
-      </c>
-      <c r="V44" s="3">
-        <v>1700</v>
       </c>
       <c r="W44" s="3">
         <v>1700</v>
@@ -4080,11 +4176,11 @@
         <v>1700</v>
       </c>
       <c r="Y44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z44" s="3">
         <v>400</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4097,8 +4193,8 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE44" s="3">
-        <v>0</v>
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF44" s="3">
         <v>0</v>
@@ -4115,8 +4211,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4147,69 +4246,69 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
-      </c>
-      <c r="V45" s="3">
-        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>800</v>
       </c>
       <c r="X45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>800</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>200</v>
       </c>
       <c r="AE45" s="3">
         <v>200</v>
       </c>
       <c r="AF45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,101 +4318,104 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E46" s="3">
         <v>50000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>41000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>30300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11400</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4323,8 +4425,11 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4355,8 +4460,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4427,13 +4532,16 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
@@ -4442,31 +4550,31 @@
         <v>200</v>
       </c>
       <c r="G48" s="3">
+        <v>200</v>
+      </c>
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
       </c>
       <c r="M48" s="3">
+        <v>200</v>
+      </c>
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100</v>
-      </c>
-      <c r="O48" s="3">
-        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
@@ -4475,7 +4583,7 @@
         <v>200</v>
       </c>
       <c r="R48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
@@ -4484,22 +4592,22 @@
         <v>300</v>
       </c>
       <c r="U48" s="3">
+        <v>300</v>
+      </c>
+      <c r="V48" s="3">
         <v>1000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>1400</v>
       </c>
       <c r="AA48" s="3">
         <v>1400</v>
@@ -4508,19 +4616,19 @@
         <v>1400</v>
       </c>
       <c r="AC48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD48" s="3">
         <v>800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>300</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>200</v>
       </c>
       <c r="AF48" s="3">
         <v>200</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
+      <c r="AG48" s="3">
+        <v>200</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
@@ -4531,55 +4639,58 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E49" s="3">
         <v>33900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3600</v>
-      </c>
-      <c r="R49" s="3">
-        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>500</v>
@@ -4588,13 +4699,13 @@
         <v>500</v>
       </c>
       <c r="U49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="V49" s="3">
         <v>600</v>
       </c>
       <c r="W49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="X49" s="3">
         <v>700</v>
@@ -4602,8 +4713,8 @@
       <c r="Y49" s="3">
         <v>700</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
+      <c r="Z49" s="3">
+        <v>700</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
@@ -4617,8 +4728,8 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4903,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -4915,7 +5035,7 @@
         <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4924,20 +5044,20 @@
         <v>0</v>
       </c>
       <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>200</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,101 +5174,104 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E54" s="3">
         <v>84000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11700</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5155,8 +5281,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,101 +5361,102 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>800</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5335,73 +5466,76 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
       </c>
       <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
         <v>4200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1600</v>
       </c>
       <c r="K58" s="3">
         <v>1600</v>
       </c>
       <c r="L58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1100</v>
-      </c>
-      <c r="S58" s="3">
-        <v>700</v>
       </c>
       <c r="T58" s="3">
         <v>700</v>
       </c>
       <c r="U58" s="3">
+        <v>700</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
-      </c>
-      <c r="V58" s="3">
-        <v>200</v>
       </c>
       <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>200</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -5418,8 +5552,8 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5439,8 +5573,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5471,69 +5608,69 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>3700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1400</v>
       </c>
       <c r="Q59" s="3">
         <v>1400</v>
       </c>
       <c r="R59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>600</v>
       </c>
       <c r="AA59" s="3">
         <v>600</v>
       </c>
       <c r="AB59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>100</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5543,101 +5680,104 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E60" s="3">
         <v>25400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>900</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5647,80 +5787,83 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E61" s="3">
         <v>30100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>4200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6400</v>
-      </c>
-      <c r="U61" s="3">
-        <v>6800</v>
       </c>
       <c r="V61" s="3">
         <v>6800</v>
       </c>
       <c r="W61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="X61" s="3">
         <v>4800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4500</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5751,20 +5894,23 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E62" s="3">
         <v>4200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5783,12 +5929,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
@@ -5802,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -5811,19 +5957,19 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
@@ -5832,20 +5978,20 @@
         <v>100</v>
       </c>
       <c r="AC62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
         <v>1600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>600</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,46 +6322,49 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E66" s="3">
         <v>59600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>51700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10300</v>
-      </c>
-      <c r="O66" s="3">
-        <v>9800</v>
       </c>
       <c r="P66" s="3">
         <v>9800</v>
@@ -6215,53 +6373,53 @@
         <v>9800</v>
       </c>
       <c r="R66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="S66" s="3">
         <v>10900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1600</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6271,8 +6429,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,17 +6769,17 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>21200</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>20400</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>19700</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,101 +6896,104 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-112100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-109500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-107900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-107300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-107900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-104900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-104100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-101800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-101200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-105800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-103100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-104000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-101000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-99400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-94100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-95200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-89100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-87000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-92200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-84500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-78000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-73200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-64200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-61500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-53300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-45900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-19800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6829,8 +7003,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,101 +7324,104 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>15500</v>
       </c>
       <c r="I76" s="3">
         <v>15500</v>
       </c>
       <c r="J76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K76" s="3">
         <v>16900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7000</v>
-      </c>
-      <c r="X76" s="3">
-        <v>10600</v>
       </c>
       <c r="Y76" s="3">
         <v>10600</v>
       </c>
       <c r="Z76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AA76" s="3">
         <v>12300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>26300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-16400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7245,8 +7431,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2" t="s">
+      <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7609,43 +7808,43 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -7654,7 +7853,7 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
@@ -7669,7 +7868,7 @@
         <v>200</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -7681,7 +7880,7 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -7701,11 +7900,14 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,16 +8586,17 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -8386,8 +8607,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -8398,32 +8619,32 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8441,22 +8662,22 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-100</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
       </c>
       <c r="AE91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG91" s="3">
         <v>-100</v>
@@ -8465,13 +8686,16 @@
         <v>-100</v>
       </c>
       <c r="AI91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ91" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,62 +8905,65 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-38100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>700</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -8747,28 +8977,28 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
       </c>
       <c r="AE94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG94" s="3">
         <v>-100</v>
@@ -8777,13 +9007,16 @@
         <v>-100</v>
       </c>
       <c r="AI94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8852,8 +9086,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,92 +9479,95 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>33600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>21200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>22000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
@@ -9329,19 +9575,22 @@
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>18000</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9372,8 +9621,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9444,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2100</v>
-      </c>
-      <c r="X102" s="3">
-        <v>300</v>
       </c>
       <c r="Y102" s="3">
         <v>300</v>
       </c>
       <c r="Z102" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>20100</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>-2300</v>
       </c>
       <c r="AE102" s="3">
         <v>-2300</v>
       </c>
       <c r="AF102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>ETON</t>
   </si>
@@ -656,264 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F8" s="3">
         <v>22500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>18900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>17300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>11600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>10300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>6100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>11900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
         <v>100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>500</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
       <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
         <v>500</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>0</v>
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK8" s="3">
         <v>0</v>
@@ -921,86 +928,92 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F9" s="3">
         <v>13300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>5800</v>
       </c>
-      <c r="F9" s="3">
-        <v>7400</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I9" s="3">
         <v>5200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>4000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>-100</v>
       </c>
-      <c r="Y9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3">
         <v>100</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,85 +1044,91 @@
       <c r="AL9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F10" s="3">
         <v>9200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>13100</v>
       </c>
-      <c r="F10" s="3">
-        <v>9900</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I10" s="3">
         <v>6500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>9700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>10300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-200</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
@@ -1141,8 +1160,14 @@
       <c r="AL10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,118 +1206,126 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>-900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>6300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>3400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>6500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>1600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>1500</v>
       </c>
-      <c r="AL12" s="3" t="s">
+      <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,29 +1434,35 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,33 +1478,33 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-400</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1478,11 +1517,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1511,13 +1550,19 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
         <v>1000</v>
@@ -1526,16 +1571,16 @@
         <v>1000</v>
       </c>
       <c r="G15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>400</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
@@ -1544,16 +1589,16 @@
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="3">
         <v>200</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1603,17 +1648,17 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1621,8 +1666,14 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1709,242 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F17" s="3">
         <v>22500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>19200</v>
       </c>
-      <c r="F17" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I17" s="3">
         <v>10600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>8700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>7300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>7500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>9000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>8100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>2800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>2200</v>
       </c>
-      <c r="AL17" s="3" t="s">
+      <c r="AN17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="O18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R18" s="3">
         <v>-2900</v>
       </c>
-      <c r="J18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>3900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>5400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-7400</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL18" s="3" t="s">
+      <c r="AN18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,8 +1983,10 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1944,71 +2011,71 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>2700</v>
       </c>
       <c r="T20" s="3">
         <v>-300</v>
       </c>
       <c r="U20" s="3">
-        <v>-100</v>
+        <v>2700</v>
       </c>
       <c r="V20" s="3">
         <v>-300</v>
       </c>
       <c r="W20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
+      <c r="AE20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>100</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
@@ -2016,130 +2083,142 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>700</v>
       </c>
-      <c r="F21" s="3">
-        <v>500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1300</v>
-      </c>
       <c r="H21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-6000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>5300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-7500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2147,40 +2226,40 @@
         <v>1000</v>
       </c>
       <c r="E22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
       </c>
       <c r="K22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2248,118 +2327,130 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-7700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL23" s="3" t="s">
+      <c r="AN23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2367,40 +2458,40 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>-100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2468,8 +2559,14 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2675,246 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-6100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>5100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-7700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL26" s="3" t="s">
+      <c r="AN26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>5100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-7700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL27" s="3" t="s">
+      <c r="AN27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +3023,14 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3018,8 +3139,14 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3255,14 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,8 +3371,14 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3264,71 +3403,71 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-2700</v>
       </c>
       <c r="T32" s="3">
         <v>300</v>
       </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>-2700</v>
       </c>
       <c r="V32" s="3">
         <v>300</v>
       </c>
       <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
+      <c r="AE32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-100</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
@@ -3336,130 +3475,142 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
-      <c r="AL32" s="3" t="s">
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>5100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-7700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL33" s="3" t="s">
+      <c r="AN33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3719,251 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>5100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-7700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL35" s="3" t="s">
+      <c r="AN35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2" t="s">
+      <c r="AN38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +4002,10 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,118 +4044,126 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F41" s="3">
         <v>37100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>25400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>14900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>20300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>16700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>22100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>14700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>16300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>17000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>15200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>14400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>22700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>25800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>25100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>21300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>7300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>12300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>12100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>11800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>14900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>19600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>26700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>6600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>8900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>11200</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4093,89 +4272,95 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F43" s="3">
         <v>13100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>16400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>300</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3">
         <v>200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4185,11 +4370,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>0</v>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI43" s="3">
         <v>0</v>
@@ -4203,89 +4388,95 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F44" s="3">
         <v>16900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>23800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>13600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>15200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>600</v>
-      </c>
-      <c r="P44" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>500</v>
       </c>
       <c r="R44" s="3">
         <v>500</v>
       </c>
       <c r="S44" s="3">
+        <v>500</v>
+      </c>
+      <c r="T44" s="3">
+        <v>500</v>
+      </c>
+      <c r="U44" s="3">
         <v>600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>300</v>
-      </c>
-      <c r="U44" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V44" s="3">
-        <v>1300</v>
       </c>
       <c r="W44" s="3">
         <v>1200</v>
       </c>
       <c r="X44" s="3">
-        <v>1700</v>
+        <v>1300</v>
       </c>
       <c r="Y44" s="3">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="Z44" s="3">
         <v>1700</v>
       </c>
       <c r="AA44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC44" s="3">
         <v>400</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4295,11 +4486,11 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>0</v>
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI44" s="3">
         <v>0</v>
@@ -4313,8 +4504,14 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4351,190 +4548,202 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>100</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>60600</v>
+      </c>
+      <c r="F46" s="3">
         <v>72000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>68400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>50000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>41000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>24300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>26800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>27200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>26300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>16400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>19800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>18800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>23600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>25900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>29100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>30300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>24700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>9800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>12800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>15300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>15000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>12100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>16800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>21500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>27500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>6800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>9200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>11400</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4571,11 +4780,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4643,34 +4852,40 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>600</v>
+      </c>
+      <c r="G48" s="3">
         <v>300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
       </c>
       <c r="I48" s="3">
+        <v>200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>200</v>
+      </c>
+      <c r="K48" s="3">
         <v>300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
@@ -4679,162 +4894,168 @@
         <v>200</v>
       </c>
       <c r="N48" s="3">
+        <v>100</v>
+      </c>
+      <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>200</v>
-      </c>
-      <c r="R48" s="3">
-        <v>200</v>
       </c>
       <c r="S48" s="3">
         <v>200</v>
       </c>
       <c r="T48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V48" s="3">
         <v>300</v>
       </c>
       <c r="W48" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="X48" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="Y48" s="3">
         <v>1000</v>
       </c>
       <c r="Z48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>1400</v>
       </c>
       <c r="AD48" s="3">
         <v>1400</v>
       </c>
       <c r="AE48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG48" s="3">
         <v>800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>200</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>30900</v>
+      </c>
+      <c r="F49" s="3">
         <v>31900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>32900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>33900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>34900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>6400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>5000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3600</v>
-      </c>
-      <c r="T49" s="3">
-        <v>500</v>
-      </c>
-      <c r="U49" s="3">
-        <v>500</v>
       </c>
       <c r="V49" s="3">
         <v>500</v>
       </c>
       <c r="W49" s="3">
+        <v>500</v>
+      </c>
+      <c r="X49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y49" s="3">
         <v>600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>600</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>700</v>
       </c>
       <c r="AA49" s="3">
         <v>700</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
+      <c r="AB49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>700</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
@@ -4845,11 +5066,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>0</v>
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
@@ -4863,8 +5084,14 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5200,14 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,13 +5316,19 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -5149,10 +5388,10 @@
         <v>0</v>
       </c>
       <c r="X52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3">
         <v>100</v>
@@ -5161,40 +5400,46 @@
         <v>100</v>
       </c>
       <c r="AB52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>200</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5548,130 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F54" s="3">
         <v>104500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>101700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>84000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>76100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>35800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>31800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>31700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>30900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>23900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>25000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>21500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>23000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>23200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>27500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>26600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>31200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>26300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>11400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>14600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>17200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>17100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>13500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>18200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>23000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>28300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>7500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>9600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>11700</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5710,10 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,109 +5752,111 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F57" s="3">
         <v>14300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>12100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>3200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1400</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>800</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>900</v>
       </c>
       <c r="AH57" s="3">
         <v>800</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ57" s="3" t="s">
-        <v>3</v>
+      <c r="AI57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ57" s="3">
+        <v>800</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>3</v>
@@ -5603,83 +5864,89 @@
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>400</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>1400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5692,11 +5959,11 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5713,20 +5980,26 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F59" s="3">
         <v>3000</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5751,53 +6024,53 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>600</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>600</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>400</v>
       </c>
       <c r="AE59" s="3">
         <v>600</v>
@@ -5806,25 +6079,31 @@
         <v>400</v>
       </c>
       <c r="AG59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI59" s="3">
         <v>300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>100</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5832,190 +6111,196 @@
         <v>44200</v>
       </c>
       <c r="E60" s="3">
+        <v>38500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>44200</v>
+      </c>
+      <c r="G60" s="3">
         <v>38600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>25400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>19900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>19700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>16200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3100</v>
-      </c>
-      <c r="V60" s="3">
-        <v>3200</v>
-      </c>
-      <c r="W60" s="3">
-        <v>3800</v>
       </c>
       <c r="X60" s="3">
         <v>3200</v>
       </c>
       <c r="Y60" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA60" s="3">
         <v>2700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>3700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>1100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>900</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F61" s="3">
         <v>28100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>27900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>30100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>29900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>4200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>6000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>5300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>5600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>6000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>6400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>4500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6043,29 +6328,35 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F62" s="3">
         <v>7400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>11200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6081,15 +6372,15 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6100,61 +6391,67 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
         <v>100</v>
       </c>
+      <c r="Y62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="AC62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD62" s="3">
         <v>100</v>
       </c>
       <c r="AE62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
         <v>1600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>600</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6560,14 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6676,14 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6792,130 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>66000</v>
+      </c>
+      <c r="F66" s="3">
         <v>81400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>77700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>59600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>51700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>19900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>18400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>16300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>9800</v>
-      </c>
-      <c r="R66" s="3">
-        <v>9800</v>
       </c>
       <c r="S66" s="3">
         <v>9800</v>
       </c>
       <c r="T66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="U66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="V66" s="3">
         <v>10900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>10700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>7500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>6500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>3800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1600</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6954,10 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +7066,14 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7182,14 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6943,28 +7278,34 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
         <v>21200</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AI70" s="3">
         <v>20400</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>19700</v>
       </c>
-      <c r="AI70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ70" s="3">
-        <v>0</v>
-      </c>
       <c r="AK70" s="3">
         <v>0</v>
       </c>
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7414,130 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-110900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-114000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-112100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-109500</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-107900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-107300</v>
       </c>
       <c r="I72" s="3">
         <v>-107900</v>
       </c>
       <c r="J72" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="K72" s="3">
+        <v>-107900</v>
+      </c>
+      <c r="L72" s="3">
         <v>-104900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-104100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-101800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-101200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-105800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-103100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-104000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-101000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-99400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-94100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-95200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-89100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-87000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-92200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-84500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-78000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-73200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-64200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-61500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-53300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-45900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7646,14 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7762,14 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7878,130 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>26200</v>
+      </c>
+      <c r="F76" s="3">
         <v>23100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>24000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>24500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>24400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>16900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16700</v>
-      </c>
-      <c r="N76" s="3">
-        <v>11200</v>
-      </c>
-      <c r="O76" s="3">
-        <v>13100</v>
       </c>
       <c r="P76" s="3">
         <v>11200</v>
       </c>
       <c r="Q76" s="3">
+        <v>13100</v>
+      </c>
+      <c r="R76" s="3">
+        <v>11200</v>
+      </c>
+      <c r="S76" s="3">
         <v>13200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>13400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>17600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>15700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>20700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>21600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>15700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>10600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>10600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>12300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>16700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>19200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>26300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-16400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-12900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>-9500</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +8110,251 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2" t="s">
+      <c r="AN80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>5100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-7700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL81" s="3" t="s">
+      <c r="AN81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,8 +8393,10 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8013,55 +8410,55 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -8073,10 +8470,10 @@
         <v>200</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
@@ -8085,10 +8482,10 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
@@ -8105,11 +8502,17 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8621,14 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8737,14 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8853,14 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8969,14 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +9085,130 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="F89" s="3">
         <v>12000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>7100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-5100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AN89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,25 +9247,27 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -8834,11 +9275,11 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -8846,35 +9287,35 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -8889,37 +9330,43 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>-100</v>
       </c>
       <c r="AI91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL91" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9475,14 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,71 +9591,77 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-38100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>700</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -9213,43 +9672,49 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-800</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>0</v>
       </c>
       <c r="AH94" s="3">
         <v>-100</v>
       </c>
       <c r="AI94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL94" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9753,10 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9326,11 +9793,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9398,8 +9865,14 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9981,14 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +10097,14 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,46 +10213,52 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>33600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-200</v>
       </c>
       <c r="J100" s="3">
         <v>-400</v>
       </c>
       <c r="K100" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="L100" s="3">
         <v>-400</v>
       </c>
       <c r="M100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>100</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -9776,58 +10267,58 @@
         <v>100</v>
       </c>
       <c r="R100" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>100</v>
       </c>
       <c r="T100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>21200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>2200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>7500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>4900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>22000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="3">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="AJ100" s="3">
         <v>0</v>
@@ -9835,11 +10326,17 @@
       <c r="AK100" s="3">
         <v>18000</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AN100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9876,11 +10373,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9948,114 +10445,126 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="F102" s="3">
         <v>11700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-8300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>3800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>14000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>20100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>16600</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AN102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
